--- a/docs/harness/wirelist/B-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/B-engine-wirelist.xlsx
@@ -2007,12 +2007,12 @@
       <c r="AD10" s="54" t="inlineStr"/>
       <c r="AE10" s="54" t="inlineStr">
         <is>
-          <t>DRB102 77 = section B c19 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'</t>
+          <t>DRB102 77 = section B c19 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'; splice sp_gndout_b_eng2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF10" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng2 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG10" s="54" t="inlineStr"/>
@@ -2122,12 +2122,12 @@
       <c r="AD11" s="38" t="inlineStr"/>
       <c r="AE11" s="38" t="inlineStr">
         <is>
-          <t>DRB102 78 = section B c21 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'</t>
+          <t>DRB102 78 = section B c21 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'; splice sp_gndout_b_eng3: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF11" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng3 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG11" s="38" t="inlineStr"/>
@@ -2814,12 +2814,12 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>DRB102 92 = section B c13 'CAN H to Link CAN-Lambda (ST185-CAN)'</t>
+          <t>DRB102 92 = section B c13 'CAN H to Link CAN-Lambda (ST185-CAN)'; splice sp_canh_lam: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh_lam is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG17" s="38" t="inlineStr">
@@ -2939,12 +2939,12 @@
       <c r="AD18" s="54" t="inlineStr"/>
       <c r="AE18" s="54" t="inlineStr">
         <is>
-          <t>DRB102 93 = section B c14 'CAN L to Link CAN-Lambda (ST185-CAN)'</t>
+          <t>DRB102 93 = section B c14 'CAN L to Link CAN-Lambda (ST185-CAN)'; splice sp_canl_lam: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF18" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl_lam is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG18" s="54" t="inlineStr">
@@ -3173,12 +3173,12 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>DRB102 95 = section B c3 'CAN-Lambda +12V, cabin fuse F5 10A (14 AWG)'</t>
+          <t>DRB102 95 = section B c3 'CAN-Lambda +12V, cabin fuse F5 10A (14 AWG)'; splice sp_lam12_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_lam12_b is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG20" s="54" t="inlineStr"/>
@@ -3288,12 +3288,12 @@
       <c r="AD21" s="38" t="inlineStr"/>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>device ref Coolant pressure — Ronybuy 150 psi pin 1 'GND'</t>
+          <t>device ref Coolant pressure — Ronybuy 150 psi pin 1 'GND'; splice sp_gndout_b_eng2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng2 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG21" s="38" t="inlineStr"/>
@@ -3401,10 +3401,14 @@
       <c r="AB22" s="53" t="inlineStr"/>
       <c r="AC22" s="54" t="inlineStr"/>
       <c r="AD22" s="54" t="inlineStr"/>
-      <c r="AE22" s="54" t="inlineStr"/>
+      <c r="AE22" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_gndout_b_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF22" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG22" s="54" t="inlineStr"/>
@@ -3514,12 +3518,12 @@
       <c r="AD23" s="38" t="inlineStr"/>
       <c r="AE23" s="38" t="inlineStr">
         <is>
-          <t>device ref Fuel pressure — Lowdoller 7990150 pin 1 'low reference/ground'</t>
+          <t>device ref Fuel pressure — Lowdoller 7990150 pin 1 'low reference/ground'; splice sp_gndout_b_eng3: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF23" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng3 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG23" s="38" t="inlineStr"/>
@@ -3960,10 +3964,14 @@
       <c r="AB27" s="37" t="inlineStr"/>
       <c r="AC27" s="38" t="inlineStr"/>
       <c r="AD27" s="38" t="inlineStr"/>
-      <c r="AE27" s="38" t="inlineStr"/>
+      <c r="AE27" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_lamg_b: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF27" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_lamg_b is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG27" s="38" t="inlineStr">
@@ -4077,12 +4085,12 @@
       <c r="AD28" s="54" t="inlineStr"/>
       <c r="AE28" s="54" t="inlineStr">
         <is>
-          <t>device ref Oil pressure — Lowdoller 7990150 pin 1 'low reference/ground'</t>
+          <t>device ref Oil pressure — Lowdoller 7990150 pin 1 'low reference/ground'; splice sp_gndout_b_eng2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF28" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng2 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG28" s="54" t="inlineStr"/>
@@ -4190,10 +4198,14 @@
       <c r="AB29" s="37" t="inlineStr"/>
       <c r="AC29" s="38" t="inlineStr"/>
       <c r="AD29" s="38" t="inlineStr"/>
-      <c r="AE29" s="38" t="inlineStr"/>
+      <c r="AE29" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_gndout_b_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF29" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG29" s="38" t="inlineStr"/>
@@ -4303,12 +4315,12 @@
       <c r="AD30" s="54" t="inlineStr"/>
       <c r="AE30" s="54" t="inlineStr">
         <is>
-          <t>device ref Gearbox VSS — Toyota 83181-20040 pin 2 'ground'</t>
+          <t>device ref Gearbox VSS — Toyota 83181-20040 pin 2 'ground'; splice sp_gndout_b_eng3: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF30" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng3 is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG30" s="54" t="inlineStr"/>
@@ -4529,10 +4541,14 @@
       <c r="AB32" s="53" t="inlineStr"/>
       <c r="AC32" s="54" t="inlineStr"/>
       <c r="AD32" s="54" t="inlineStr"/>
-      <c r="AE32" s="54" t="inlineStr"/>
+      <c r="AE32" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_gndout_b_eng2: node of the wire list (SoT); splice sp_gndout_b_eng: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF32" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_gndout_b_eng2 is not named in the SoT (drawing only); splice sp_gndout_b_eng is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG32" s="54" t="inlineStr"/>
@@ -4640,10 +4656,14 @@
       <c r="AB33" s="37" t="inlineStr"/>
       <c r="AC33" s="38" t="inlineStr"/>
       <c r="AD33" s="38" t="inlineStr"/>
-      <c r="AE33" s="38" t="inlineStr"/>
+      <c r="AE33" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_lam12_b: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF33" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_lam12_b is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG33" s="38" t="inlineStr">
@@ -4753,12 +4773,12 @@
       <c r="AD34" s="54" t="inlineStr"/>
       <c r="AE34" s="54" t="inlineStr">
         <is>
-          <t>DRB102 96 = section B c4 'CAN-Lambda ground to cabin chassis ground (14 AWG)'</t>
+          <t>splice sp_lamg_b: node of the wire list (SoT); DRB102 96 = section B c4 'CAN-Lambda ground to cabin chassis ground (14 AWG)'</t>
         </is>
       </c>
       <c r="AF34" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_lamg_b is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG34" s="54" t="inlineStr"/>
@@ -7366,7 +7386,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7442,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7498,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7554,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7610,7 @@
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/B-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/B-engine-wirelist.xlsx
@@ -3142,7 +3142,7 @@
       </c>
       <c r="R20" s="47" t="inlineStr">
         <is>
-          <t>+12V LAM 7.5A (LOGIC BUS2-1)</t>
+          <t>+12V CAN-Lambda +12 V (LOGIC BUS2-1)</t>
         </is>
       </c>
       <c r="S20" s="48" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="R33" s="31" t="inlineStr">
         <is>
-          <t>+12V LAM 7.5A (LOGIC BUS2-1)</t>
+          <t>+12V CAN-Lambda +12 V (LOGIC BUS2-1)</t>
         </is>
       </c>
       <c r="S33" s="32" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="E6" s="47" t="inlineStr">
         <is>
-          <t>+12V LAM 7.5A (LOGIC BUS2-1)</t>
+          <t>+12V CAN-Lambda +12 V (LOGIC BUS2-1)</t>
         </is>
       </c>
       <c r="F6" s="48" t="n">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="I23" s="59" t="inlineStr">
         <is>
-          <t>+12V LAM 7.5A (LOGIC BUS2-1)</t>
+          <t>+12V CAN-Lambda +12 V (LOGIC BUS2-1)</t>
         </is>
       </c>
       <c r="J23" s="60" t="inlineStr">

--- a/docs/harness/wirelist/B-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/B-engine-wirelist.xlsx
@@ -3022,12 +3022,12 @@
       <c r="P19" s="29" t="inlineStr"/>
       <c r="Q19" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R19" s="31" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="S19" s="32" t="inlineStr"/>
@@ -3058,7 +3058,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to B17, via the CAN sc'</t>
+          <t>DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to ECU C1, via the CAN'</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="I22" s="61" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="J22" s="62" t="inlineStr">

--- a/docs/harness/wirelist/B-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/B-engine-wirelist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG67"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="H3" s="25" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="I3" s="26" t="inlineStr">
         <is>
@@ -1184,12 +1184,12 @@
       <c r="P3" s="29" t="inlineStr"/>
       <c r="Q3" s="30" t="inlineStr">
         <is>
-          <t>DRB102.62</t>
+          <t>DRB102.77</t>
         </is>
       </c>
       <c r="R3" s="31" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in (DRB102 62)</t>
+          <t>Back-up sw +12 V in (DRB102 77)</t>
         </is>
       </c>
       <c r="S3" s="32" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
       <c r="AD3" s="38" t="inlineStr"/>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>DRB102 62 = section B c25 'Back-up switch B1 pin 2 feed &lt;- J/B No.1 GAUGE 15A'</t>
+          <t>DRB102 77 = loom B c77 'Back-up sw +12 V in'</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="H4" s="41" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>DRB102 71 = section B c7 'ECU-B B15'; device ref Oil pressure — Lowdoller 7990150 pin 3 'signal'</t>
+          <t>DRB102 28 = loom B c28 'ECU-B B15'; device ref Oil pressure — Lowdoller 7990150 pin 3 'signal'</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="H5" s="25" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>DRB102 72 = section B c8 'ECU-B B16'; device ref Fuel pressure — Lowdoller 7990150 pin 3 'signal'</t>
+          <t>DRB102 14 = loom B c14 'ECU-B B16'; device ref Fuel pressure — Lowdoller 7990150 pin 3 'signal'</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="H6" s="41" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
       <c r="AD6" s="54" t="inlineStr"/>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>DRB102 73 = section B c9 'ECU-B B23'; device ref Coolant pressure — Ronybuy 150 psi pin 3 'Output'</t>
+          <t>DRB102 26 = loom B c26 'ECU-B B23'; device ref Coolant pressure — Ronybuy 150 psi pin 3 'Output'</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="H7" s="25" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       <c r="AD7" s="38" t="inlineStr"/>
       <c r="AE7" s="38" t="inlineStr">
         <is>
-          <t>DRB102 74 = section B c10 'ECU-B B6'</t>
+          <t>DRB102 61 = loom B c61 'ECU-B B6'</t>
         </is>
       </c>
       <c r="AF7" s="38" t="inlineStr">
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="H8" s="41" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       <c r="AD8" s="54" t="inlineStr"/>
       <c r="AE8" s="54" t="inlineStr">
         <is>
-          <t>DRB102 75 = section B c11 'ECU-B B7'</t>
+          <t>DRB102 59 = loom B c59 'ECU-B B7'</t>
         </is>
       </c>
       <c r="AF8" s="54" t="inlineStr">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="H9" s="25" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I9" s="26" t="inlineStr">
         <is>
@@ -1854,12 +1854,12 @@
       <c r="P9" s="29" t="inlineStr"/>
       <c r="Q9" s="30" t="inlineStr">
         <is>
-          <t>DRB102.76</t>
+          <t>DRB102.78</t>
         </is>
       </c>
       <c r="R9" s="31" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out (DRB102 76)</t>
+          <t>Reverse sw +12 V out (DRB102 78)</t>
         </is>
       </c>
       <c r="S9" s="32" t="inlineStr"/>
@@ -1892,7 +1892,7 @@
       <c r="AD9" s="38" t="inlineStr"/>
       <c r="AE9" s="38" t="inlineStr">
         <is>
-          <t>DRB102 76 = section B c12 'Back-up switch B1 pin 1 out (+12V in reverse) -&gt; r'</t>
+          <t>DRB102 78 = loom B c78 'Reverse sw +12 V out'</t>
         </is>
       </c>
       <c r="AF9" s="38" t="inlineStr">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="H10" s="41" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="I10" s="42" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       <c r="AD10" s="54" t="inlineStr"/>
       <c r="AE10" s="54" t="inlineStr">
         <is>
-          <t>DRB102 77 = section B c19 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'; splice sp_gndout_b_eng2: node of the wire list (SoT)</t>
+          <t>DRB102 29 = loom B c29 'Gnd oil/clnt/temps'; splice sp_gndout_b_eng2: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF10" s="54" t="inlineStr">
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="H11" s="25" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
       <c r="AD11" s="38" t="inlineStr"/>
       <c r="AE11" s="38" t="inlineStr">
         <is>
-          <t>DRB102 78 = section B c21 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'; splice sp_gndout_b_eng3: node of the wire list (SoT)</t>
+          <t>DRB102 15 = loom B c15 'Gnd fuel press + VSS'; splice sp_gndout_b_eng3: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF11" s="38" t="inlineStr">
@@ -2165,7 +2165,7 @@
         </is>
       </c>
       <c r="H12" s="41" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I12" s="42" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
       <c r="AD12" s="54" t="inlineStr"/>
       <c r="AE12" s="54" t="inlineStr">
         <is>
-          <t>DRB102 83 = section B c16 'Knock 1 SIG+ (ECU B9)'</t>
+          <t>DRB102 71 = loom B c71 'ECU-B B9'</t>
         </is>
       </c>
       <c r="AF12" s="54" t="inlineStr">
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="H13" s="25" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I13" s="26" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       <c r="AD13" s="38" t="inlineStr"/>
       <c r="AE13" s="38" t="inlineStr">
         <is>
-          <t>DRB102 84 = section B c17 'Knock 1 SIG- (to Gnd Out B22)'</t>
+          <t>DRB102 72 = loom B c72 'Knock sensor (-)'</t>
         </is>
       </c>
       <c r="AF13" s="38" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="H14" s="41" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I14" s="42" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>DRB102 85 = section B c18 'Knock 1 screen'</t>
+          <t>DRB102 73 = loom B c73 'Knock sensor shield'</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="H15" s="25" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       <c r="AD15" s="38" t="inlineStr"/>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>DRB102 90 = section B c20 'Switched 12V to gearbox VSS (from sp_sw12)'; device ref Gearbox VSS — Toyota 83181-20040 pin 1 'IG +12V switched'</t>
+          <t>DRB102 67 = loom B c67 '+12 V gearbox speed'; device ref Gearbox VSS — Toyota 83181-20040 pin 1 'IG +12V switched'</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="H16" s="41" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="I16" s="42" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>DRB102 91 = section B c23 'Gearbox VSS screen (to B17)'</t>
+          <t>DRB102 69 = loom B c69 'Gearbox speed shield'</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="H17" s="25" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>DRB102 92 = section B c13 'CAN H to Link CAN-Lambda (ST185-CAN)'; splice sp_canh_lam: node of the wire list (SoT)</t>
+          <t>DRB102 79 = loom B c79 'CAN H to CAN-Lambda'; splice sp_canh_lam: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="H18" s="41" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I18" s="42" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
       <c r="AD18" s="54" t="inlineStr"/>
       <c r="AE18" s="54" t="inlineStr">
         <is>
-          <t>DRB102 93 = section B c14 'CAN L to Link CAN-Lambda (ST185-CAN)'; splice sp_canl_lam: node of the wire list (SoT)</t>
+          <t>DRB102 80 = loom B c80 'CAN L to CAN-Lambda'; splice sp_canl_lam: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF18" s="54" t="inlineStr">
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="H19" s="25" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to ECU C1, via the CAN'</t>
+          <t>DRB102 81 = loom B c81 'CAN-Lambda shield'</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -3173,7 +3173,7 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>DRB102 95 = section B c3 'CAN-Lambda +12V, cabin fuse F5 10A (14 AWG)'; splice sp_lam12_b: node of the wire list (SoT)</t>
+          <t>DRB102 95 = loom B c95 'CAN-Lambda +12 V'; splice sp_lam12_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="N31" s="28" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="O31" s="29" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
       <c r="AD31" s="38" t="inlineStr"/>
       <c r="AE31" s="38" t="inlineStr">
         <is>
-          <t>device ref Gearbox VSS — Toyota 83181-20040 pin 3 'SP1 speed output'; DRB102 89 = section B c15 'Gearbox VSS signal (ECU B29, DI 8)'</t>
+          <t>device ref Gearbox VSS — Toyota 83181-20040 pin 3 'SP1 speed output'; DRB102 68 = loom B c68 'ECU-B B29'</t>
         </is>
       </c>
       <c r="AF31" s="38" t="inlineStr">
@@ -4773,7 +4773,7 @@
       <c r="AD34" s="54" t="inlineStr"/>
       <c r="AE34" s="54" t="inlineStr">
         <is>
-          <t>splice sp_lamg_b: node of the wire list (SoT); DRB102 96 = section B c4 'CAN-Lambda ground to cabin chassis ground (14 AWG)'</t>
+          <t>splice sp_lamg_b: node of the wire list (SoT); DRB102 96 = loom B c96 'CAN-Lambda ground'</t>
         </is>
       </c>
       <c r="AF34" s="54" t="inlineStr">
@@ -4799,16 +4799,16 @@
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>bh_b_eng</t>
+          <t>ix_brail_p</t>
         </is>
       </c>
       <c r="G35" s="26" t="inlineStr">
         <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
+          <t>IX-B-RAIL inline socket, +5 V from A-engine</t>
         </is>
       </c>
       <c r="H35" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="26" t="inlineStr">
         <is>
@@ -4824,12 +4824,12 @@
       <c r="P35" s="29" t="inlineStr"/>
       <c r="Q35" s="30" t="inlineStr">
         <is>
-          <t>DRB102.3</t>
+          <t>ix_brail_p.4</t>
         </is>
       </c>
       <c r="R35" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 3)</t>
+          <t>spare (ix_brail_p 4)</t>
         </is>
       </c>
       <c r="S35" s="32" t="inlineStr"/>
@@ -4844,11 +4844,7 @@
       <c r="AB35" s="37" t="inlineStr"/>
       <c r="AC35" s="38" t="inlineStr"/>
       <c r="AD35" s="38" t="inlineStr"/>
-      <c r="AE35" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 3 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE35" s="38" t="inlineStr"/>
       <c r="AF35" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4872,16 +4868,16 @@
       </c>
       <c r="F36" s="41" t="inlineStr">
         <is>
-          <t>bh_b_eng</t>
+          <t>ix_brail_p</t>
         </is>
       </c>
       <c r="G36" s="42" t="inlineStr">
         <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
+          <t>IX-B-RAIL inline socket, +5 V from A-engine</t>
         </is>
       </c>
       <c r="H36" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="42" t="inlineStr">
         <is>
@@ -4897,12 +4893,12 @@
       <c r="P36" s="45" t="inlineStr"/>
       <c r="Q36" s="46" t="inlineStr">
         <is>
-          <t>DRB102.4</t>
+          <t>ix_brail_p.5</t>
         </is>
       </c>
       <c r="R36" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 4)</t>
+          <t>spare (ix_brail_p 5)</t>
         </is>
       </c>
       <c r="S36" s="48" t="inlineStr"/>
@@ -4917,11 +4913,7 @@
       <c r="AB36" s="53" t="inlineStr"/>
       <c r="AC36" s="54" t="inlineStr"/>
       <c r="AD36" s="54" t="inlineStr"/>
-      <c r="AE36" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 4 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE36" s="54" t="inlineStr"/>
       <c r="AF36" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -4945,16 +4937,16 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>bh_b_eng</t>
+          <t>ix_brail_p</t>
         </is>
       </c>
       <c r="G37" s="26" t="inlineStr">
         <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
+          <t>IX-B-RAIL inline socket, +5 V from A-engine</t>
         </is>
       </c>
       <c r="H37" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" s="26" t="inlineStr">
         <is>
@@ -4970,12 +4962,12 @@
       <c r="P37" s="29" t="inlineStr"/>
       <c r="Q37" s="30" t="inlineStr">
         <is>
-          <t>DRB102.5</t>
+          <t>ix_brail_p.6</t>
         </is>
       </c>
       <c r="R37" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 5)</t>
+          <t>spare (ix_brail_p 6)</t>
         </is>
       </c>
       <c r="S37" s="32" t="inlineStr"/>
@@ -4990,11 +4982,7 @@
       <c r="AB37" s="37" t="inlineStr"/>
       <c r="AC37" s="38" t="inlineStr"/>
       <c r="AD37" s="38" t="inlineStr"/>
-      <c r="AE37" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 5 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE37" s="38" t="inlineStr"/>
       <c r="AF37" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5027,7 +5015,7 @@
         </is>
       </c>
       <c r="H38" s="41" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="I38" s="42" t="inlineStr">
         <is>
@@ -5043,12 +5031,12 @@
       <c r="P38" s="45" t="inlineStr"/>
       <c r="Q38" s="46" t="inlineStr">
         <is>
-          <t>DRB102.6</t>
+          <t>DRB102.51</t>
         </is>
       </c>
       <c r="R38" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 6)</t>
+          <t>spare (DRB102 51)</t>
         </is>
       </c>
       <c r="S38" s="48" t="inlineStr"/>
@@ -5065,7 +5053,7 @@
       <c r="AD38" s="54" t="inlineStr"/>
       <c r="AE38" s="54" t="inlineStr">
         <is>
-          <t>DRB102 6 = 'spare (size 12)'</t>
+          <t>DRB102 51 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF38" s="54" t="inlineStr">
@@ -5100,7 +5088,7 @@
         </is>
       </c>
       <c r="H39" s="25" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="I39" s="26" t="inlineStr">
         <is>
@@ -5116,12 +5104,12 @@
       <c r="P39" s="29" t="inlineStr"/>
       <c r="Q39" s="30" t="inlineStr">
         <is>
-          <t>DRB102.7</t>
+          <t>DRB102.60</t>
         </is>
       </c>
       <c r="R39" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 7)</t>
+          <t>spare (DRB102 60)</t>
         </is>
       </c>
       <c r="S39" s="32" t="inlineStr"/>
@@ -5138,7 +5126,7 @@
       <c r="AD39" s="38" t="inlineStr"/>
       <c r="AE39" s="38" t="inlineStr">
         <is>
-          <t>DRB102 7 = 'spare (size 12)'</t>
+          <t>DRB102 60 = 'spare (size 4)'</t>
         </is>
       </c>
       <c r="AF39" s="38" t="inlineStr">
@@ -5173,7 +5161,7 @@
         </is>
       </c>
       <c r="H40" s="41" t="n">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="I40" s="42" t="inlineStr">
         <is>
@@ -5189,12 +5177,12 @@
       <c r="P40" s="45" t="inlineStr"/>
       <c r="Q40" s="46" t="inlineStr">
         <is>
-          <t>DRB102.8</t>
+          <t>DRB102.62</t>
         </is>
       </c>
       <c r="R40" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 8)</t>
+          <t>spare (DRB102 62)</t>
         </is>
       </c>
       <c r="S40" s="48" t="inlineStr"/>
@@ -5211,7 +5199,7 @@
       <c r="AD40" s="54" t="inlineStr"/>
       <c r="AE40" s="54" t="inlineStr">
         <is>
-          <t>DRB102 8 = 'spare (size 12)'</t>
+          <t>DRB102 62 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF40" s="54" t="inlineStr">
@@ -5246,7 +5234,7 @@
         </is>
       </c>
       <c r="H41" s="25" t="n">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="I41" s="26" t="inlineStr">
         <is>
@@ -5262,12 +5250,12 @@
       <c r="P41" s="29" t="inlineStr"/>
       <c r="Q41" s="30" t="inlineStr">
         <is>
-          <t>DRB102.43</t>
+          <t>DRB102.82</t>
         </is>
       </c>
       <c r="R41" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 43)</t>
+          <t>spare (DRB102 82)</t>
         </is>
       </c>
       <c r="S41" s="32" t="inlineStr"/>
@@ -5284,7 +5272,7 @@
       <c r="AD41" s="38" t="inlineStr"/>
       <c r="AE41" s="38" t="inlineStr">
         <is>
-          <t>DRB102 43 = 'spare (size 4)'</t>
+          <t>DRB102 82 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF41" s="38" t="inlineStr">
@@ -5319,7 +5307,7 @@
         </is>
       </c>
       <c r="H42" s="41" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="I42" s="42" t="inlineStr">
         <is>
@@ -5335,12 +5323,12 @@
       <c r="P42" s="45" t="inlineStr"/>
       <c r="Q42" s="46" t="inlineStr">
         <is>
-          <t>DRB102.48</t>
+          <t>DRB102.97</t>
         </is>
       </c>
       <c r="R42" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 48)</t>
+          <t>spare (DRB102 97)</t>
         </is>
       </c>
       <c r="S42" s="48" t="inlineStr"/>
@@ -5357,7 +5345,7 @@
       <c r="AD42" s="54" t="inlineStr"/>
       <c r="AE42" s="54" t="inlineStr">
         <is>
-          <t>DRB102 48 = 'spare (size 8)'</t>
+          <t>DRB102 97 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF42" s="54" t="inlineStr">
@@ -5392,7 +5380,7 @@
         </is>
       </c>
       <c r="H43" s="25" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="I43" s="26" t="inlineStr">
         <is>
@@ -5408,12 +5396,12 @@
       <c r="P43" s="29" t="inlineStr"/>
       <c r="Q43" s="30" t="inlineStr">
         <is>
-          <t>DRB102.49</t>
+          <t>DRB102.98</t>
         </is>
       </c>
       <c r="R43" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 49)</t>
+          <t>spare (DRB102 98)</t>
         </is>
       </c>
       <c r="S43" s="32" t="inlineStr"/>
@@ -5430,7 +5418,7 @@
       <c r="AD43" s="38" t="inlineStr"/>
       <c r="AE43" s="38" t="inlineStr">
         <is>
-          <t>DRB102 49 = 'spare (size 8)'</t>
+          <t>DRB102 98 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF43" s="38" t="inlineStr">
@@ -5465,7 +5453,7 @@
         </is>
       </c>
       <c r="H44" s="41" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="I44" s="42" t="inlineStr">
         <is>
@@ -5481,12 +5469,12 @@
       <c r="P44" s="45" t="inlineStr"/>
       <c r="Q44" s="46" t="inlineStr">
         <is>
-          <t>DRB102.54</t>
+          <t>DRB102.99</t>
         </is>
       </c>
       <c r="R44" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 54)</t>
+          <t>spare (DRB102 99)</t>
         </is>
       </c>
       <c r="S44" s="48" t="inlineStr"/>
@@ -5503,7 +5491,7 @@
       <c r="AD44" s="54" t="inlineStr"/>
       <c r="AE44" s="54" t="inlineStr">
         <is>
-          <t>DRB102 54 = 'spare (size 8)'</t>
+          <t>DRB102 99 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF44" s="54" t="inlineStr">
@@ -5538,7 +5526,7 @@
         </is>
       </c>
       <c r="H45" s="25" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I45" s="26" t="inlineStr">
         <is>
@@ -5554,12 +5542,12 @@
       <c r="P45" s="29" t="inlineStr"/>
       <c r="Q45" s="30" t="inlineStr">
         <is>
-          <t>DRB102.55</t>
+          <t>DRB102.100</t>
         </is>
       </c>
       <c r="R45" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 55)</t>
+          <t>spare (DRB102 100)</t>
         </is>
       </c>
       <c r="S45" s="32" t="inlineStr"/>
@@ -5576,7 +5564,7 @@
       <c r="AD45" s="38" t="inlineStr"/>
       <c r="AE45" s="38" t="inlineStr">
         <is>
-          <t>DRB102 55 = 'spare (size 8)'</t>
+          <t>DRB102 100 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF45" s="38" t="inlineStr">
@@ -5611,7 +5599,7 @@
         </is>
       </c>
       <c r="H46" s="41" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="I46" s="42" t="inlineStr">
         <is>
@@ -5627,12 +5615,12 @@
       <c r="P46" s="45" t="inlineStr"/>
       <c r="Q46" s="46" t="inlineStr">
         <is>
-          <t>DRB102.60</t>
+          <t>DRB102.101</t>
         </is>
       </c>
       <c r="R46" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 60)</t>
+          <t>spare (DRB102 101)</t>
         </is>
       </c>
       <c r="S46" s="48" t="inlineStr"/>
@@ -5649,7 +5637,7 @@
       <c r="AD46" s="54" t="inlineStr"/>
       <c r="AE46" s="54" t="inlineStr">
         <is>
-          <t>DRB102 60 = 'spare (size 4)'</t>
+          <t>DRB102 101 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF46" s="54" t="inlineStr">
@@ -5684,7 +5672,7 @@
         </is>
       </c>
       <c r="H47" s="25" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I47" s="26" t="inlineStr">
         <is>
@@ -5700,12 +5688,12 @@
       <c r="P47" s="29" t="inlineStr"/>
       <c r="Q47" s="30" t="inlineStr">
         <is>
-          <t>DRB102.63</t>
+          <t>DRB102.102</t>
         </is>
       </c>
       <c r="R47" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 63)</t>
+          <t>spare (DRB102 102)</t>
         </is>
       </c>
       <c r="S47" s="32" t="inlineStr"/>
@@ -5722,7 +5710,7 @@
       <c r="AD47" s="38" t="inlineStr"/>
       <c r="AE47" s="38" t="inlineStr">
         <is>
-          <t>DRB102 63 = 'spare (size 16)'</t>
+          <t>DRB102 102 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF47" s="38" t="inlineStr">
@@ -5732,1456 +5720,8 @@
       </c>
       <c r="AG47" s="38" t="inlineStr"/>
     </row>
-    <row r="48">
-      <c r="A48" s="39" t="inlineStr"/>
-      <c r="B48" s="39" t="inlineStr"/>
-      <c r="C48" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D48" s="39" t="inlineStr"/>
-      <c r="E48" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F48" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G48" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H48" s="41" t="n">
-        <v>64</v>
-      </c>
-      <c r="I48" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J48" s="42" t="inlineStr"/>
-      <c r="K48" s="43" t="inlineStr"/>
-      <c r="L48" s="44" t="inlineStr"/>
-      <c r="M48" s="45" t="inlineStr"/>
-      <c r="N48" s="44" t="inlineStr"/>
-      <c r="O48" s="45" t="inlineStr"/>
-      <c r="P48" s="45" t="inlineStr"/>
-      <c r="Q48" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.64</t>
-        </is>
-      </c>
-      <c r="R48" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 64)</t>
-        </is>
-      </c>
-      <c r="S48" s="48" t="inlineStr"/>
-      <c r="T48" s="48" t="inlineStr"/>
-      <c r="U48" s="49" t="inlineStr"/>
-      <c r="V48" s="50" t="inlineStr"/>
-      <c r="W48" s="50" t="inlineStr"/>
-      <c r="X48" s="50" t="inlineStr"/>
-      <c r="Y48" s="50" t="inlineStr"/>
-      <c r="Z48" s="51" t="inlineStr"/>
-      <c r="AA48" s="52" t="inlineStr"/>
-      <c r="AB48" s="53" t="inlineStr"/>
-      <c r="AC48" s="54" t="inlineStr"/>
-      <c r="AD48" s="54" t="inlineStr"/>
-      <c r="AE48" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 64 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF48" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG48" s="54" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="23" t="inlineStr"/>
-      <c r="B49" s="23" t="inlineStr"/>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D49" s="23" t="inlineStr"/>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F49" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G49" s="26" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H49" s="25" t="n">
-        <v>65</v>
-      </c>
-      <c r="I49" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J49" s="26" t="inlineStr"/>
-      <c r="K49" s="27" t="inlineStr"/>
-      <c r="L49" s="28" t="inlineStr"/>
-      <c r="M49" s="29" t="inlineStr"/>
-      <c r="N49" s="28" t="inlineStr"/>
-      <c r="O49" s="29" t="inlineStr"/>
-      <c r="P49" s="29" t="inlineStr"/>
-      <c r="Q49" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.65</t>
-        </is>
-      </c>
-      <c r="R49" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 65)</t>
-        </is>
-      </c>
-      <c r="S49" s="32" t="inlineStr"/>
-      <c r="T49" s="32" t="inlineStr"/>
-      <c r="U49" s="33" t="inlineStr"/>
-      <c r="V49" s="34" t="inlineStr"/>
-      <c r="W49" s="34" t="inlineStr"/>
-      <c r="X49" s="34" t="inlineStr"/>
-      <c r="Y49" s="34" t="inlineStr"/>
-      <c r="Z49" s="35" t="inlineStr"/>
-      <c r="AA49" s="36" t="inlineStr"/>
-      <c r="AB49" s="37" t="inlineStr"/>
-      <c r="AC49" s="38" t="inlineStr"/>
-      <c r="AD49" s="38" t="inlineStr"/>
-      <c r="AE49" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 65 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF49" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG49" s="38" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="39" t="inlineStr"/>
-      <c r="B50" s="39" t="inlineStr"/>
-      <c r="C50" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D50" s="39" t="inlineStr"/>
-      <c r="E50" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F50" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G50" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H50" s="41" t="n">
-        <v>66</v>
-      </c>
-      <c r="I50" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J50" s="42" t="inlineStr"/>
-      <c r="K50" s="43" t="inlineStr"/>
-      <c r="L50" s="44" t="inlineStr"/>
-      <c r="M50" s="45" t="inlineStr"/>
-      <c r="N50" s="44" t="inlineStr"/>
-      <c r="O50" s="45" t="inlineStr"/>
-      <c r="P50" s="45" t="inlineStr"/>
-      <c r="Q50" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.66</t>
-        </is>
-      </c>
-      <c r="R50" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 66)</t>
-        </is>
-      </c>
-      <c r="S50" s="48" t="inlineStr"/>
-      <c r="T50" s="48" t="inlineStr"/>
-      <c r="U50" s="49" t="inlineStr"/>
-      <c r="V50" s="50" t="inlineStr"/>
-      <c r="W50" s="50" t="inlineStr"/>
-      <c r="X50" s="50" t="inlineStr"/>
-      <c r="Y50" s="50" t="inlineStr"/>
-      <c r="Z50" s="51" t="inlineStr"/>
-      <c r="AA50" s="52" t="inlineStr"/>
-      <c r="AB50" s="53" t="inlineStr"/>
-      <c r="AC50" s="54" t="inlineStr"/>
-      <c r="AD50" s="54" t="inlineStr"/>
-      <c r="AE50" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 66 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF50" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG50" s="54" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="23" t="inlineStr"/>
-      <c r="B51" s="23" t="inlineStr"/>
-      <c r="C51" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D51" s="23" t="inlineStr"/>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F51" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G51" s="26" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H51" s="25" t="n">
-        <v>67</v>
-      </c>
-      <c r="I51" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J51" s="26" t="inlineStr"/>
-      <c r="K51" s="27" t="inlineStr"/>
-      <c r="L51" s="28" t="inlineStr"/>
-      <c r="M51" s="29" t="inlineStr"/>
-      <c r="N51" s="28" t="inlineStr"/>
-      <c r="O51" s="29" t="inlineStr"/>
-      <c r="P51" s="29" t="inlineStr"/>
-      <c r="Q51" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.67</t>
-        </is>
-      </c>
-      <c r="R51" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 67)</t>
-        </is>
-      </c>
-      <c r="S51" s="32" t="inlineStr"/>
-      <c r="T51" s="32" t="inlineStr"/>
-      <c r="U51" s="33" t="inlineStr"/>
-      <c r="V51" s="34" t="inlineStr"/>
-      <c r="W51" s="34" t="inlineStr"/>
-      <c r="X51" s="34" t="inlineStr"/>
-      <c r="Y51" s="34" t="inlineStr"/>
-      <c r="Z51" s="35" t="inlineStr"/>
-      <c r="AA51" s="36" t="inlineStr"/>
-      <c r="AB51" s="37" t="inlineStr"/>
-      <c r="AC51" s="38" t="inlineStr"/>
-      <c r="AD51" s="38" t="inlineStr"/>
-      <c r="AE51" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 67 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF51" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG51" s="38" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="39" t="inlineStr"/>
-      <c r="B52" s="39" t="inlineStr"/>
-      <c r="C52" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D52" s="39" t="inlineStr"/>
-      <c r="E52" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F52" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G52" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H52" s="41" t="n">
-        <v>68</v>
-      </c>
-      <c r="I52" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J52" s="42" t="inlineStr"/>
-      <c r="K52" s="43" t="inlineStr"/>
-      <c r="L52" s="44" t="inlineStr"/>
-      <c r="M52" s="45" t="inlineStr"/>
-      <c r="N52" s="44" t="inlineStr"/>
-      <c r="O52" s="45" t="inlineStr"/>
-      <c r="P52" s="45" t="inlineStr"/>
-      <c r="Q52" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.68</t>
-        </is>
-      </c>
-      <c r="R52" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 68)</t>
-        </is>
-      </c>
-      <c r="S52" s="48" t="inlineStr"/>
-      <c r="T52" s="48" t="inlineStr"/>
-      <c r="U52" s="49" t="inlineStr"/>
-      <c r="V52" s="50" t="inlineStr"/>
-      <c r="W52" s="50" t="inlineStr"/>
-      <c r="X52" s="50" t="inlineStr"/>
-      <c r="Y52" s="50" t="inlineStr"/>
-      <c r="Z52" s="51" t="inlineStr"/>
-      <c r="AA52" s="52" t="inlineStr"/>
-      <c r="AB52" s="53" t="inlineStr"/>
-      <c r="AC52" s="54" t="inlineStr"/>
-      <c r="AD52" s="54" t="inlineStr"/>
-      <c r="AE52" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 68 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF52" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG52" s="54" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="23" t="inlineStr"/>
-      <c r="B53" s="23" t="inlineStr"/>
-      <c r="C53" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D53" s="23" t="inlineStr"/>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F53" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G53" s="26" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H53" s="25" t="n">
-        <v>69</v>
-      </c>
-      <c r="I53" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J53" s="26" t="inlineStr"/>
-      <c r="K53" s="27" t="inlineStr"/>
-      <c r="L53" s="28" t="inlineStr"/>
-      <c r="M53" s="29" t="inlineStr"/>
-      <c r="N53" s="28" t="inlineStr"/>
-      <c r="O53" s="29" t="inlineStr"/>
-      <c r="P53" s="29" t="inlineStr"/>
-      <c r="Q53" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.69</t>
-        </is>
-      </c>
-      <c r="R53" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 69)</t>
-        </is>
-      </c>
-      <c r="S53" s="32" t="inlineStr"/>
-      <c r="T53" s="32" t="inlineStr"/>
-      <c r="U53" s="33" t="inlineStr"/>
-      <c r="V53" s="34" t="inlineStr"/>
-      <c r="W53" s="34" t="inlineStr"/>
-      <c r="X53" s="34" t="inlineStr"/>
-      <c r="Y53" s="34" t="inlineStr"/>
-      <c r="Z53" s="35" t="inlineStr"/>
-      <c r="AA53" s="36" t="inlineStr"/>
-      <c r="AB53" s="37" t="inlineStr"/>
-      <c r="AC53" s="38" t="inlineStr"/>
-      <c r="AD53" s="38" t="inlineStr"/>
-      <c r="AE53" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 69 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF53" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG53" s="38" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="39" t="inlineStr"/>
-      <c r="B54" s="39" t="inlineStr"/>
-      <c r="C54" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D54" s="39" t="inlineStr"/>
-      <c r="E54" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F54" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G54" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H54" s="41" t="n">
-        <v>70</v>
-      </c>
-      <c r="I54" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J54" s="42" t="inlineStr"/>
-      <c r="K54" s="43" t="inlineStr"/>
-      <c r="L54" s="44" t="inlineStr"/>
-      <c r="M54" s="45" t="inlineStr"/>
-      <c r="N54" s="44" t="inlineStr"/>
-      <c r="O54" s="45" t="inlineStr"/>
-      <c r="P54" s="45" t="inlineStr"/>
-      <c r="Q54" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.70</t>
-        </is>
-      </c>
-      <c r="R54" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 70)</t>
-        </is>
-      </c>
-      <c r="S54" s="48" t="inlineStr"/>
-      <c r="T54" s="48" t="inlineStr"/>
-      <c r="U54" s="49" t="inlineStr"/>
-      <c r="V54" s="50" t="inlineStr"/>
-      <c r="W54" s="50" t="inlineStr"/>
-      <c r="X54" s="50" t="inlineStr"/>
-      <c r="Y54" s="50" t="inlineStr"/>
-      <c r="Z54" s="51" t="inlineStr"/>
-      <c r="AA54" s="52" t="inlineStr"/>
-      <c r="AB54" s="53" t="inlineStr"/>
-      <c r="AC54" s="54" t="inlineStr"/>
-      <c r="AD54" s="54" t="inlineStr"/>
-      <c r="AE54" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 70 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF54" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG54" s="54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="23" t="inlineStr"/>
-      <c r="B55" s="23" t="inlineStr"/>
-      <c r="C55" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D55" s="23" t="inlineStr"/>
-      <c r="E55" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F55" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G55" s="26" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H55" s="25" t="n">
-        <v>79</v>
-      </c>
-      <c r="I55" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J55" s="26" t="inlineStr"/>
-      <c r="K55" s="27" t="inlineStr"/>
-      <c r="L55" s="28" t="inlineStr"/>
-      <c r="M55" s="29" t="inlineStr"/>
-      <c r="N55" s="28" t="inlineStr"/>
-      <c r="O55" s="29" t="inlineStr"/>
-      <c r="P55" s="29" t="inlineStr"/>
-      <c r="Q55" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.79</t>
-        </is>
-      </c>
-      <c r="R55" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 79)</t>
-        </is>
-      </c>
-      <c r="S55" s="32" t="inlineStr"/>
-      <c r="T55" s="32" t="inlineStr"/>
-      <c r="U55" s="33" t="inlineStr"/>
-      <c r="V55" s="34" t="inlineStr"/>
-      <c r="W55" s="34" t="inlineStr"/>
-      <c r="X55" s="34" t="inlineStr"/>
-      <c r="Y55" s="34" t="inlineStr"/>
-      <c r="Z55" s="35" t="inlineStr"/>
-      <c r="AA55" s="36" t="inlineStr"/>
-      <c r="AB55" s="37" t="inlineStr"/>
-      <c r="AC55" s="38" t="inlineStr"/>
-      <c r="AD55" s="38" t="inlineStr"/>
-      <c r="AE55" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 79 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF55" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG55" s="38" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="39" t="inlineStr"/>
-      <c r="B56" s="39" t="inlineStr"/>
-      <c r="C56" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D56" s="39" t="inlineStr"/>
-      <c r="E56" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F56" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G56" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H56" s="41" t="n">
-        <v>80</v>
-      </c>
-      <c r="I56" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J56" s="42" t="inlineStr"/>
-      <c r="K56" s="43" t="inlineStr"/>
-      <c r="L56" s="44" t="inlineStr"/>
-      <c r="M56" s="45" t="inlineStr"/>
-      <c r="N56" s="44" t="inlineStr"/>
-      <c r="O56" s="45" t="inlineStr"/>
-      <c r="P56" s="45" t="inlineStr"/>
-      <c r="Q56" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.80</t>
-        </is>
-      </c>
-      <c r="R56" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 80)</t>
-        </is>
-      </c>
-      <c r="S56" s="48" t="inlineStr"/>
-      <c r="T56" s="48" t="inlineStr"/>
-      <c r="U56" s="49" t="inlineStr"/>
-      <c r="V56" s="50" t="inlineStr"/>
-      <c r="W56" s="50" t="inlineStr"/>
-      <c r="X56" s="50" t="inlineStr"/>
-      <c r="Y56" s="50" t="inlineStr"/>
-      <c r="Z56" s="51" t="inlineStr"/>
-      <c r="AA56" s="52" t="inlineStr"/>
-      <c r="AB56" s="53" t="inlineStr"/>
-      <c r="AC56" s="54" t="inlineStr"/>
-      <c r="AD56" s="54" t="inlineStr"/>
-      <c r="AE56" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 80 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF56" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG56" s="54" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="23" t="inlineStr"/>
-      <c r="B57" s="23" t="inlineStr"/>
-      <c r="C57" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D57" s="23" t="inlineStr"/>
-      <c r="E57" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F57" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G57" s="26" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H57" s="25" t="n">
-        <v>81</v>
-      </c>
-      <c r="I57" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J57" s="26" t="inlineStr"/>
-      <c r="K57" s="27" t="inlineStr"/>
-      <c r="L57" s="28" t="inlineStr"/>
-      <c r="M57" s="29" t="inlineStr"/>
-      <c r="N57" s="28" t="inlineStr"/>
-      <c r="O57" s="29" t="inlineStr"/>
-      <c r="P57" s="29" t="inlineStr"/>
-      <c r="Q57" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.81</t>
-        </is>
-      </c>
-      <c r="R57" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 81)</t>
-        </is>
-      </c>
-      <c r="S57" s="32" t="inlineStr"/>
-      <c r="T57" s="32" t="inlineStr"/>
-      <c r="U57" s="33" t="inlineStr"/>
-      <c r="V57" s="34" t="inlineStr"/>
-      <c r="W57" s="34" t="inlineStr"/>
-      <c r="X57" s="34" t="inlineStr"/>
-      <c r="Y57" s="34" t="inlineStr"/>
-      <c r="Z57" s="35" t="inlineStr"/>
-      <c r="AA57" s="36" t="inlineStr"/>
-      <c r="AB57" s="37" t="inlineStr"/>
-      <c r="AC57" s="38" t="inlineStr"/>
-      <c r="AD57" s="38" t="inlineStr"/>
-      <c r="AE57" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 81 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF57" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG57" s="38" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="39" t="inlineStr"/>
-      <c r="B58" s="39" t="inlineStr"/>
-      <c r="C58" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D58" s="39" t="inlineStr"/>
-      <c r="E58" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F58" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G58" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H58" s="41" t="n">
-        <v>82</v>
-      </c>
-      <c r="I58" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J58" s="42" t="inlineStr"/>
-      <c r="K58" s="43" t="inlineStr"/>
-      <c r="L58" s="44" t="inlineStr"/>
-      <c r="M58" s="45" t="inlineStr"/>
-      <c r="N58" s="44" t="inlineStr"/>
-      <c r="O58" s="45" t="inlineStr"/>
-      <c r="P58" s="45" t="inlineStr"/>
-      <c r="Q58" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.82</t>
-        </is>
-      </c>
-      <c r="R58" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 82)</t>
-        </is>
-      </c>
-      <c r="S58" s="48" t="inlineStr"/>
-      <c r="T58" s="48" t="inlineStr"/>
-      <c r="U58" s="49" t="inlineStr"/>
-      <c r="V58" s="50" t="inlineStr"/>
-      <c r="W58" s="50" t="inlineStr"/>
-      <c r="X58" s="50" t="inlineStr"/>
-      <c r="Y58" s="50" t="inlineStr"/>
-      <c r="Z58" s="51" t="inlineStr"/>
-      <c r="AA58" s="52" t="inlineStr"/>
-      <c r="AB58" s="53" t="inlineStr"/>
-      <c r="AC58" s="54" t="inlineStr"/>
-      <c r="AD58" s="54" t="inlineStr"/>
-      <c r="AE58" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 82 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF58" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG58" s="54" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="23" t="inlineStr"/>
-      <c r="B59" s="23" t="inlineStr"/>
-      <c r="C59" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D59" s="23" t="inlineStr"/>
-      <c r="E59" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F59" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G59" s="26" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H59" s="25" t="n">
-        <v>97</v>
-      </c>
-      <c r="I59" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J59" s="26" t="inlineStr"/>
-      <c r="K59" s="27" t="inlineStr"/>
-      <c r="L59" s="28" t="inlineStr"/>
-      <c r="M59" s="29" t="inlineStr"/>
-      <c r="N59" s="28" t="inlineStr"/>
-      <c r="O59" s="29" t="inlineStr"/>
-      <c r="P59" s="29" t="inlineStr"/>
-      <c r="Q59" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.97</t>
-        </is>
-      </c>
-      <c r="R59" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 97)</t>
-        </is>
-      </c>
-      <c r="S59" s="32" t="inlineStr"/>
-      <c r="T59" s="32" t="inlineStr"/>
-      <c r="U59" s="33" t="inlineStr"/>
-      <c r="V59" s="34" t="inlineStr"/>
-      <c r="W59" s="34" t="inlineStr"/>
-      <c r="X59" s="34" t="inlineStr"/>
-      <c r="Y59" s="34" t="inlineStr"/>
-      <c r="Z59" s="35" t="inlineStr"/>
-      <c r="AA59" s="36" t="inlineStr"/>
-      <c r="AB59" s="37" t="inlineStr"/>
-      <c r="AC59" s="38" t="inlineStr"/>
-      <c r="AD59" s="38" t="inlineStr"/>
-      <c r="AE59" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 97 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF59" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG59" s="38" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="39" t="inlineStr"/>
-      <c r="B60" s="39" t="inlineStr"/>
-      <c r="C60" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D60" s="39" t="inlineStr"/>
-      <c r="E60" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F60" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G60" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H60" s="41" t="n">
-        <v>98</v>
-      </c>
-      <c r="I60" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J60" s="42" t="inlineStr"/>
-      <c r="K60" s="43" t="inlineStr"/>
-      <c r="L60" s="44" t="inlineStr"/>
-      <c r="M60" s="45" t="inlineStr"/>
-      <c r="N60" s="44" t="inlineStr"/>
-      <c r="O60" s="45" t="inlineStr"/>
-      <c r="P60" s="45" t="inlineStr"/>
-      <c r="Q60" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.98</t>
-        </is>
-      </c>
-      <c r="R60" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 98)</t>
-        </is>
-      </c>
-      <c r="S60" s="48" t="inlineStr"/>
-      <c r="T60" s="48" t="inlineStr"/>
-      <c r="U60" s="49" t="inlineStr"/>
-      <c r="V60" s="50" t="inlineStr"/>
-      <c r="W60" s="50" t="inlineStr"/>
-      <c r="X60" s="50" t="inlineStr"/>
-      <c r="Y60" s="50" t="inlineStr"/>
-      <c r="Z60" s="51" t="inlineStr"/>
-      <c r="AA60" s="52" t="inlineStr"/>
-      <c r="AB60" s="53" t="inlineStr"/>
-      <c r="AC60" s="54" t="inlineStr"/>
-      <c r="AD60" s="54" t="inlineStr"/>
-      <c r="AE60" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 98 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF60" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG60" s="54" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="23" t="inlineStr"/>
-      <c r="B61" s="23" t="inlineStr"/>
-      <c r="C61" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D61" s="23" t="inlineStr"/>
-      <c r="E61" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F61" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G61" s="26" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H61" s="25" t="n">
-        <v>99</v>
-      </c>
-      <c r="I61" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J61" s="26" t="inlineStr"/>
-      <c r="K61" s="27" t="inlineStr"/>
-      <c r="L61" s="28" t="inlineStr"/>
-      <c r="M61" s="29" t="inlineStr"/>
-      <c r="N61" s="28" t="inlineStr"/>
-      <c r="O61" s="29" t="inlineStr"/>
-      <c r="P61" s="29" t="inlineStr"/>
-      <c r="Q61" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.99</t>
-        </is>
-      </c>
-      <c r="R61" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 99)</t>
-        </is>
-      </c>
-      <c r="S61" s="32" t="inlineStr"/>
-      <c r="T61" s="32" t="inlineStr"/>
-      <c r="U61" s="33" t="inlineStr"/>
-      <c r="V61" s="34" t="inlineStr"/>
-      <c r="W61" s="34" t="inlineStr"/>
-      <c r="X61" s="34" t="inlineStr"/>
-      <c r="Y61" s="34" t="inlineStr"/>
-      <c r="Z61" s="35" t="inlineStr"/>
-      <c r="AA61" s="36" t="inlineStr"/>
-      <c r="AB61" s="37" t="inlineStr"/>
-      <c r="AC61" s="38" t="inlineStr"/>
-      <c r="AD61" s="38" t="inlineStr"/>
-      <c r="AE61" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 99 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF61" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG61" s="38" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="39" t="inlineStr"/>
-      <c r="B62" s="39" t="inlineStr"/>
-      <c r="C62" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D62" s="39" t="inlineStr"/>
-      <c r="E62" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F62" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G62" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H62" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I62" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J62" s="42" t="inlineStr"/>
-      <c r="K62" s="43" t="inlineStr"/>
-      <c r="L62" s="44" t="inlineStr"/>
-      <c r="M62" s="45" t="inlineStr"/>
-      <c r="N62" s="44" t="inlineStr"/>
-      <c r="O62" s="45" t="inlineStr"/>
-      <c r="P62" s="45" t="inlineStr"/>
-      <c r="Q62" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.100</t>
-        </is>
-      </c>
-      <c r="R62" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 100)</t>
-        </is>
-      </c>
-      <c r="S62" s="48" t="inlineStr"/>
-      <c r="T62" s="48" t="inlineStr"/>
-      <c r="U62" s="49" t="inlineStr"/>
-      <c r="V62" s="50" t="inlineStr"/>
-      <c r="W62" s="50" t="inlineStr"/>
-      <c r="X62" s="50" t="inlineStr"/>
-      <c r="Y62" s="50" t="inlineStr"/>
-      <c r="Z62" s="51" t="inlineStr"/>
-      <c r="AA62" s="52" t="inlineStr"/>
-      <c r="AB62" s="53" t="inlineStr"/>
-      <c r="AC62" s="54" t="inlineStr"/>
-      <c r="AD62" s="54" t="inlineStr"/>
-      <c r="AE62" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 100 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF62" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG62" s="54" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="23" t="inlineStr"/>
-      <c r="B63" s="23" t="inlineStr"/>
-      <c r="C63" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D63" s="23" t="inlineStr"/>
-      <c r="E63" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F63" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G63" s="26" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H63" s="25" t="n">
-        <v>101</v>
-      </c>
-      <c r="I63" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J63" s="26" t="inlineStr"/>
-      <c r="K63" s="27" t="inlineStr"/>
-      <c r="L63" s="28" t="inlineStr"/>
-      <c r="M63" s="29" t="inlineStr"/>
-      <c r="N63" s="28" t="inlineStr"/>
-      <c r="O63" s="29" t="inlineStr"/>
-      <c r="P63" s="29" t="inlineStr"/>
-      <c r="Q63" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.101</t>
-        </is>
-      </c>
-      <c r="R63" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 101)</t>
-        </is>
-      </c>
-      <c r="S63" s="32" t="inlineStr"/>
-      <c r="T63" s="32" t="inlineStr"/>
-      <c r="U63" s="33" t="inlineStr"/>
-      <c r="V63" s="34" t="inlineStr"/>
-      <c r="W63" s="34" t="inlineStr"/>
-      <c r="X63" s="34" t="inlineStr"/>
-      <c r="Y63" s="34" t="inlineStr"/>
-      <c r="Z63" s="35" t="inlineStr"/>
-      <c r="AA63" s="36" t="inlineStr"/>
-      <c r="AB63" s="37" t="inlineStr"/>
-      <c r="AC63" s="38" t="inlineStr"/>
-      <c r="AD63" s="38" t="inlineStr"/>
-      <c r="AE63" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 101 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF63" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG63" s="38" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="39" t="inlineStr"/>
-      <c r="B64" s="39" t="inlineStr"/>
-      <c r="C64" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D64" s="39" t="inlineStr"/>
-      <c r="E64" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F64" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_eng</t>
-        </is>
-      </c>
-      <c r="G64" s="42" t="inlineStr">
-        <is>
-          <t>Bulkhead BH-B (DRB102, RH firewall)</t>
-        </is>
-      </c>
-      <c r="H64" s="41" t="n">
-        <v>102</v>
-      </c>
-      <c r="I64" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J64" s="42" t="inlineStr"/>
-      <c r="K64" s="43" t="inlineStr"/>
-      <c r="L64" s="44" t="inlineStr"/>
-      <c r="M64" s="45" t="inlineStr"/>
-      <c r="N64" s="44" t="inlineStr"/>
-      <c r="O64" s="45" t="inlineStr"/>
-      <c r="P64" s="45" t="inlineStr"/>
-      <c r="Q64" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.102</t>
-        </is>
-      </c>
-      <c r="R64" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 102)</t>
-        </is>
-      </c>
-      <c r="S64" s="48" t="inlineStr"/>
-      <c r="T64" s="48" t="inlineStr"/>
-      <c r="U64" s="49" t="inlineStr"/>
-      <c r="V64" s="50" t="inlineStr"/>
-      <c r="W64" s="50" t="inlineStr"/>
-      <c r="X64" s="50" t="inlineStr"/>
-      <c r="Y64" s="50" t="inlineStr"/>
-      <c r="Z64" s="51" t="inlineStr"/>
-      <c r="AA64" s="52" t="inlineStr"/>
-      <c r="AB64" s="53" t="inlineStr"/>
-      <c r="AC64" s="54" t="inlineStr"/>
-      <c r="AD64" s="54" t="inlineStr"/>
-      <c r="AE64" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 102 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF64" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG64" s="54" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="23" t="inlineStr"/>
-      <c r="B65" s="23" t="inlineStr"/>
-      <c r="C65" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D65" s="23" t="inlineStr"/>
-      <c r="E65" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F65" s="25" t="inlineStr">
-        <is>
-          <t>ix_brail_p</t>
-        </is>
-      </c>
-      <c r="G65" s="26" t="inlineStr">
-        <is>
-          <t>IX-B-RAIL inline socket, +5 V from A-engine</t>
-        </is>
-      </c>
-      <c r="H65" s="25" t="n">
-        <v>4</v>
-      </c>
-      <c r="I65" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J65" s="26" t="inlineStr"/>
-      <c r="K65" s="27" t="inlineStr"/>
-      <c r="L65" s="28" t="inlineStr"/>
-      <c r="M65" s="29" t="inlineStr"/>
-      <c r="N65" s="28" t="inlineStr"/>
-      <c r="O65" s="29" t="inlineStr"/>
-      <c r="P65" s="29" t="inlineStr"/>
-      <c r="Q65" s="30" t="inlineStr">
-        <is>
-          <t>ix_brail_p.4</t>
-        </is>
-      </c>
-      <c r="R65" s="31" t="inlineStr">
-        <is>
-          <t>spare (ix_brail_p 4)</t>
-        </is>
-      </c>
-      <c r="S65" s="32" t="inlineStr"/>
-      <c r="T65" s="32" t="inlineStr"/>
-      <c r="U65" s="33" t="inlineStr"/>
-      <c r="V65" s="34" t="inlineStr"/>
-      <c r="W65" s="34" t="inlineStr"/>
-      <c r="X65" s="34" t="inlineStr"/>
-      <c r="Y65" s="34" t="inlineStr"/>
-      <c r="Z65" s="35" t="inlineStr"/>
-      <c r="AA65" s="36" t="inlineStr"/>
-      <c r="AB65" s="37" t="inlineStr"/>
-      <c r="AC65" s="38" t="inlineStr"/>
-      <c r="AD65" s="38" t="inlineStr"/>
-      <c r="AE65" s="38" t="inlineStr"/>
-      <c r="AF65" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG65" s="38" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="39" t="inlineStr"/>
-      <c r="B66" s="39" t="inlineStr"/>
-      <c r="C66" s="39" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D66" s="39" t="inlineStr"/>
-      <c r="E66" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F66" s="41" t="inlineStr">
-        <is>
-          <t>ix_brail_p</t>
-        </is>
-      </c>
-      <c r="G66" s="42" t="inlineStr">
-        <is>
-          <t>IX-B-RAIL inline socket, +5 V from A-engine</t>
-        </is>
-      </c>
-      <c r="H66" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="I66" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J66" s="42" t="inlineStr"/>
-      <c r="K66" s="43" t="inlineStr"/>
-      <c r="L66" s="44" t="inlineStr"/>
-      <c r="M66" s="45" t="inlineStr"/>
-      <c r="N66" s="44" t="inlineStr"/>
-      <c r="O66" s="45" t="inlineStr"/>
-      <c r="P66" s="45" t="inlineStr"/>
-      <c r="Q66" s="46" t="inlineStr">
-        <is>
-          <t>ix_brail_p.5</t>
-        </is>
-      </c>
-      <c r="R66" s="47" t="inlineStr">
-        <is>
-          <t>spare (ix_brail_p 5)</t>
-        </is>
-      </c>
-      <c r="S66" s="48" t="inlineStr"/>
-      <c r="T66" s="48" t="inlineStr"/>
-      <c r="U66" s="49" t="inlineStr"/>
-      <c r="V66" s="50" t="inlineStr"/>
-      <c r="W66" s="50" t="inlineStr"/>
-      <c r="X66" s="50" t="inlineStr"/>
-      <c r="Y66" s="50" t="inlineStr"/>
-      <c r="Z66" s="51" t="inlineStr"/>
-      <c r="AA66" s="52" t="inlineStr"/>
-      <c r="AB66" s="53" t="inlineStr"/>
-      <c r="AC66" s="54" t="inlineStr"/>
-      <c r="AD66" s="54" t="inlineStr"/>
-      <c r="AE66" s="54" t="inlineStr"/>
-      <c r="AF66" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG66" s="54" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="23" t="inlineStr"/>
-      <c r="B67" s="23" t="inlineStr"/>
-      <c r="C67" s="23" t="inlineStr">
-        <is>
-          <t>B-engine</t>
-        </is>
-      </c>
-      <c r="D67" s="23" t="inlineStr"/>
-      <c r="E67" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F67" s="25" t="inlineStr">
-        <is>
-          <t>ix_brail_p</t>
-        </is>
-      </c>
-      <c r="G67" s="26" t="inlineStr">
-        <is>
-          <t>IX-B-RAIL inline socket, +5 V from A-engine</t>
-        </is>
-      </c>
-      <c r="H67" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="I67" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J67" s="26" t="inlineStr"/>
-      <c r="K67" s="27" t="inlineStr"/>
-      <c r="L67" s="28" t="inlineStr"/>
-      <c r="M67" s="29" t="inlineStr"/>
-      <c r="N67" s="28" t="inlineStr"/>
-      <c r="O67" s="29" t="inlineStr"/>
-      <c r="P67" s="29" t="inlineStr"/>
-      <c r="Q67" s="30" t="inlineStr">
-        <is>
-          <t>ix_brail_p.6</t>
-        </is>
-      </c>
-      <c r="R67" s="31" t="inlineStr">
-        <is>
-          <t>spare (ix_brail_p 6)</t>
-        </is>
-      </c>
-      <c r="S67" s="32" t="inlineStr"/>
-      <c r="T67" s="32" t="inlineStr"/>
-      <c r="U67" s="33" t="inlineStr"/>
-      <c r="V67" s="34" t="inlineStr"/>
-      <c r="W67" s="34" t="inlineStr"/>
-      <c r="X67" s="34" t="inlineStr"/>
-      <c r="Y67" s="34" t="inlineStr"/>
-      <c r="Z67" s="35" t="inlineStr"/>
-      <c r="AA67" s="36" t="inlineStr"/>
-      <c r="AB67" s="37" t="inlineStr"/>
-      <c r="AC67" s="38" t="inlineStr"/>
-      <c r="AD67" s="38" t="inlineStr"/>
-      <c r="AE67" s="38" t="inlineStr"/>
-      <c r="AF67" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG67" s="38" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:AG67"/>
+  <autoFilter ref="A2:AG47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -7342,7 +5882,7 @@
       </c>
       <c r="B3" s="55" t="inlineStr">
         <is>
-          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 77 splice</t>
+          <t>Sensor return splice - oil temp and charge temp, tied to the BH-B pin 29 splice</t>
         </is>
       </c>
       <c r="C3" s="23" t="inlineStr">
@@ -7398,7 +5938,7 @@
       </c>
       <c r="B4" s="57" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 77 (ECU B22) to oil and coolant pressure</t>
+          <t>Sensor return splice - BH-B pin 29 (ECU B22) to oil and coolant pressure</t>
         </is>
       </c>
       <c r="C4" s="39" t="inlineStr">
@@ -7454,7 +5994,7 @@
       </c>
       <c r="B5" s="55" t="inlineStr">
         <is>
-          <t>Sensor return splice - BH-B pin 78 (ECU B22) to fuel pressure and gearbox speed</t>
+          <t>Sensor return splice - BH-B pin 15 (ECU B22) to fuel pressure and gearbox speed</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
@@ -7744,7 +6284,7 @@
       </c>
       <c r="G3" s="36" t="inlineStr">
         <is>
-          <t>shared DRB102 (section B here, section A on A-engine)</t>
+          <t>shared DRB102 (loom B wires here, loom A wires on A-engine)</t>
         </is>
       </c>
     </row>
@@ -8137,7 +6677,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D3" s="26" t="inlineStr">
         <is>
@@ -8155,7 +6695,7 @@
         </is>
       </c>
       <c r="G3" s="28" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="H3" s="29" t="inlineStr">
         <is>
@@ -8185,7 +6725,7 @@
         </is>
       </c>
       <c r="C4" s="41" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="D4" s="42" t="inlineStr">
         <is>
@@ -8203,7 +6743,7 @@
         </is>
       </c>
       <c r="G4" s="44" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="H4" s="45" t="inlineStr">
         <is>
@@ -8233,7 +6773,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
@@ -8251,7 +6791,7 @@
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
@@ -8281,7 +6821,7 @@
         </is>
       </c>
       <c r="C6" s="41" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
@@ -8299,7 +6839,7 @@
         </is>
       </c>
       <c r="G6" s="44" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="H6" s="45" t="inlineStr">
         <is>
@@ -8308,7 +6848,7 @@
       </c>
       <c r="I6" s="61" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in (DRB102 62)</t>
+          <t>Back-up sw +12 V in (DRB102 77)</t>
         </is>
       </c>
       <c r="J6" s="62" t="inlineStr">
@@ -8329,7 +6869,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
@@ -8347,7 +6887,7 @@
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
@@ -8377,7 +6917,7 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
@@ -8395,7 +6935,7 @@
         </is>
       </c>
       <c r="G8" s="44" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="H8" s="45" t="inlineStr">
         <is>
@@ -8425,7 +6965,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
@@ -8443,7 +6983,7 @@
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
@@ -8473,7 +7013,7 @@
         </is>
       </c>
       <c r="C10" s="41" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
@@ -8491,7 +7031,7 @@
         </is>
       </c>
       <c r="G10" s="44" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H10" s="45" t="inlineStr">
         <is>
@@ -8521,7 +7061,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
@@ -8539,7 +7079,7 @@
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
@@ -8569,7 +7109,7 @@
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
@@ -8587,7 +7127,7 @@
         </is>
       </c>
       <c r="G12" s="44" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H12" s="45" t="inlineStr">
         <is>
@@ -8596,7 +7136,7 @@
       </c>
       <c r="I12" s="61" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out (DRB102 76)</t>
+          <t>Reverse sw +12 V out (DRB102 78)</t>
         </is>
       </c>
       <c r="J12" s="62" t="inlineStr">
@@ -8617,7 +7157,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
@@ -8635,7 +7175,7 @@
         </is>
       </c>
       <c r="G13" s="28" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
@@ -8665,7 +7205,7 @@
         </is>
       </c>
       <c r="C14" s="41" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D14" s="42" t="inlineStr">
         <is>
@@ -8683,7 +7223,7 @@
         </is>
       </c>
       <c r="G14" s="44" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="H14" s="45" t="inlineStr">
         <is>
@@ -8713,7 +7253,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
@@ -8731,7 +7271,7 @@
         </is>
       </c>
       <c r="G15" s="28" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H15" s="29" t="inlineStr">
         <is>
@@ -8761,7 +7301,7 @@
         </is>
       </c>
       <c r="C16" s="41" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
@@ -8779,7 +7319,7 @@
         </is>
       </c>
       <c r="G16" s="44" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H16" s="45" t="inlineStr">
         <is>
@@ -8809,7 +7349,7 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
@@ -8827,7 +7367,7 @@
         </is>
       </c>
       <c r="G17" s="28" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
@@ -8857,7 +7397,7 @@
         </is>
       </c>
       <c r="C18" s="41" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D18" s="42" t="inlineStr">
         <is>
@@ -8875,7 +7415,7 @@
         </is>
       </c>
       <c r="G18" s="44" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="H18" s="45" t="inlineStr">
         <is>
@@ -8905,7 +7445,7 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
@@ -8923,7 +7463,7 @@
         </is>
       </c>
       <c r="G19" s="28" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
@@ -8953,7 +7493,7 @@
         </is>
       </c>
       <c r="C20" s="41" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D20" s="42" t="inlineStr">
         <is>
@@ -8971,7 +7511,7 @@
         </is>
       </c>
       <c r="G20" s="44" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H20" s="45" t="inlineStr">
         <is>
@@ -9001,7 +7541,7 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
@@ -9019,7 +7559,7 @@
         </is>
       </c>
       <c r="G21" s="28" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
@@ -9049,7 +7589,7 @@
         </is>
       </c>
       <c r="C22" s="41" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D22" s="42" t="inlineStr">
         <is>
@@ -9067,7 +7607,7 @@
         </is>
       </c>
       <c r="G22" s="44" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H22" s="45" t="inlineStr">
         <is>
@@ -9145,7 +7685,7 @@
         </is>
       </c>
       <c r="C24" s="41" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D24" s="42" t="inlineStr">
         <is>
@@ -9163,7 +7703,7 @@
         </is>
       </c>
       <c r="G24" s="44" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="H24" s="45" t="inlineStr">
         <is>

--- a/docs/harness/wirelist/B-engine-wirelist.xlsx
+++ b/docs/harness/wirelist/B-engine-wirelist.xlsx
@@ -1202,11 +1202,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W3" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W3" s="34" t="inlineStr"/>
       <c r="X3" s="34" t="inlineStr">
         <is>
           <t>White</t>
@@ -1647,7 +1643,7 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W7" s="34" t="inlineStr"/>
@@ -1758,7 +1754,7 @@
       </c>
       <c r="V8" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W8" s="50" t="inlineStr"/>
@@ -1869,14 +1865,10 @@
       </c>
       <c r="V9" s="34" t="inlineStr">
         <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="W9" s="34" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W9" s="34" t="inlineStr"/>
       <c r="X9" s="34" t="inlineStr">
         <is>
           <t>White</t>
@@ -1986,14 +1978,10 @@
       </c>
       <c r="V10" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W10" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W10" s="50" t="inlineStr"/>
       <c r="X10" s="50" t="inlineStr">
         <is>
           <t>Yellow-Blue</t>
@@ -2101,14 +2089,10 @@
       </c>
       <c r="V11" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W11" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W11" s="34" t="inlineStr"/>
       <c r="X11" s="34" t="inlineStr">
         <is>
           <t>Yellow-Blue</t>
@@ -3267,14 +3251,10 @@
       </c>
       <c r="V21" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W21" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W21" s="34" t="inlineStr"/>
       <c r="X21" s="34" t="inlineStr">
         <is>
           <t>Yellow-White</t>
@@ -3382,14 +3362,10 @@
       </c>
       <c r="V22" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W22" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W22" s="50" t="inlineStr"/>
       <c r="X22" s="50" t="inlineStr">
         <is>
           <t>White-Blue</t>
@@ -3497,14 +3473,10 @@
       </c>
       <c r="V23" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W23" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W23" s="34" t="inlineStr"/>
       <c r="X23" s="34" t="inlineStr">
         <is>
           <t>White-Yellow</t>
@@ -4064,14 +4036,10 @@
       </c>
       <c r="V28" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W28" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W28" s="50" t="inlineStr"/>
       <c r="X28" s="50" t="inlineStr">
         <is>
           <t>White-White</t>
@@ -4179,14 +4147,10 @@
       </c>
       <c r="V29" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W29" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W29" s="34" t="inlineStr"/>
       <c r="X29" s="34" t="inlineStr">
         <is>
           <t>Blue-Blue-Blue</t>
@@ -4522,14 +4486,10 @@
       </c>
       <c r="V32" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W32" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W32" s="50" t="inlineStr"/>
       <c r="X32" s="50" t="inlineStr">
         <is>
           <t>Yellow-Blue</t>
